--- a/docs/reports/DEMO.xlsx
+++ b/docs/reports/DEMO.xlsx
@@ -8,15 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDM" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS (reported)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS (reported)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF (reported)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS (reported)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS (reported)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF (reported)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,15 +27,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +98,12 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -137,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,21 +156,25 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,9 +187,9 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Industrials · Standard (FCFF-DCF led) · generated 2026-07-04 · data: DEMO (synthetic)</t>
+          <t>Industrials · Standard (forward multiples + DCF) · generated 2026-10-13 · data: DEMO (synthetic)</t>
         </is>
       </c>
     </row>
@@ -577,7 +590,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -599,11 +612,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>182.9753039200974</v>
+        <v>294.2009389878127</v>
       </c>
     </row>
     <row r="8">
@@ -665,6 +678,454 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMO — IS (reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As reported by DEMO (synthetic) (USDmm). Hardcoded actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>58000</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>64380.00000000001</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>70174.20000000001</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>75086.39400000001</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>81093.30552000001</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>85958.90385120003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>EBIT (operating income)</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>15080</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>17060.7</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>18947.034</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>20648.75835000001</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>22706.12554560001</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>24498.28759759201</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>18096</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>20408.46</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>22596.09240000001</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>24553.25083800001</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>26922.97743264001</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>28968.15059785441</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>3016</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>3347.760000000001</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>3649.0584</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>3904.492488</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>4216.85188704</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>4469.863000262401</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>550</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>550</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>550</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>550</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>550</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Pre-tax income</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>14730</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>16710.7</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>18597.034</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>20298.75835000001</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>22356.12554560001</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>24148.28759759201</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Tax expense</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>2798.7</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>3175.033000000001</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>3533.436460000001</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>3856.764086500001</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>4247.663853664001</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>4588.174643542482</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>11931.3</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>13535.667</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>15063.59754</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>16441.9942635</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>18108.46169193601</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>19560.11295404953</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMO — BS (reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As reported by DEMO (synthetic) (USDmm). Hardcoded actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Cash &amp; ST investments</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>10100</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>10700</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Minority interest</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -697,37 +1158,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -739,22 +1200,22 @@
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="25" t="n">
         <v>14947.3</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="25" t="n">
         <v>16883.427</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="25" t="n">
         <v>18712.65594</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="25" t="n">
         <v>20346.48675150001</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="25" t="n">
         <v>22325.31357897601</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="25" t="n">
         <v>24029.97595431193</v>
       </c>
     </row>
@@ -764,22 +1225,22 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="25" t="n">
         <v>2784</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="25" t="n">
         <v>3090.240000000001</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="25" t="n">
         <v>3368.361600000001</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="25" t="n">
         <v>3604.146912000001</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="25" t="n">
         <v>3892.478664960001</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="25" t="n">
         <v>4126.027384857602</v>
       </c>
     </row>
@@ -789,22 +1250,22 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="25" t="n">
         <v>696</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="25" t="n">
         <v>772.5600000000002</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="25" t="n">
         <v>842.0904000000003</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="25" t="n">
         <v>901.0367280000003</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="25" t="n">
         <v>973.1196662400002</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="25" t="n">
         <v>1031.5068462144</v>
       </c>
     </row>
@@ -819,7 +1280,728 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMO — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>intrinsic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>230.2679444300176</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>195.7932446575796</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>270.3739636759826</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>299.2740923153946</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>245.4047556986235</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>353.1434289321656</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>308.7672151725392</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>253.2128006520085</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>364.32162969307</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>SUMPRODUCT(C5:C7,F5:F7)/SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.09258863852952992</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>$B$10*(1+$B$11)-$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Street mean target</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Street weight in target</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>(1-$B$15)*$B$13+$B$15*$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>294.2009389878127</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Target anchored 30% to the Street consensus ($285.00, 24 analysts); model-only target $298.14.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMO — projected P&amp;L &amp; levered FCF (DCF base case)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Revenue (mn)</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>91976.02712078404</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>97242.50107360962</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>101922.3637284257</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>106160.1062143977</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>110075.7571630058</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>113765.450065953</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>117304.4019366943</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>120750.5996737408</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>124148.3572415785</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>127252.0661726179</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="12">
+        <f>C5/B5-1</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>D5/C5-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>E5/D5-1</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>F5/E5-1</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>G5/F5-1</f>
+        <v/>
+      </c>
+      <c r="H6" s="12">
+        <f>H5/G5-1</f>
+        <v/>
+      </c>
+      <c r="I6" s="12">
+        <f>I5/H5-1</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EBIT margin</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0.2869081058999161</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.2862906156470625</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.285673125394209</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.2850556351413554</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.2844381448885019</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.2838206546356483</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.2832031643827948</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.2825856741299412</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.2825856741299412</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.2825856741299412</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EBIT (mn)</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>B5*B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="18">
+        <f>C5*C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>D5*D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>E5*E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="18">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="18">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="18">
+        <f>K5*K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Net income (mn)</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>20929.320860833</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>22104.5885545333</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>23138.84895703044</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>24066.3445679313</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>24915.3927733605</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>25708.57745523674</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>26463.49203784749</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>27193.63558442294</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>27971.36325082134</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>28681.78483209187</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>B9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>C9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>D9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>E9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>F9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>G9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="H10" s="16">
+        <f>H9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="I10" s="16">
+        <f>I9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="J10" s="16">
+        <f>J9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>K9*1000000/1520000000.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Levered FCF (mn)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>20305.78018192693</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>21526.39523626225</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>22567.06019833192</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>23467.17211944108</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>24260.42425119743</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>24974.21862353873</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>25630.12755568923</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>26244.76841823402</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>26892.84857617929</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>27508.67422075087</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>FCF margin</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B12/B5</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>C12/C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>D12/D5</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>E12/E5</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>F12/F5</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>G12/G5</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
+        <f>H12/H5</f>
+        <v/>
+      </c>
+      <c r="I13" s="12">
+        <f>I12/I5</f>
+        <v/>
+      </c>
+      <c r="J13" s="12">
+        <f>J12/J5</f>
+        <v/>
+      </c>
+      <c r="K13" s="12">
+        <f>K12/K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -845,7 +2027,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: DEMO (synthetic), retrieved 2026-07-04.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: DEMO (synthetic), retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -863,7 +2045,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
@@ -872,7 +2054,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="20" t="n">
         <v>1520</v>
       </c>
     </row>
@@ -882,7 +2064,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="20" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -892,7 +2074,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="20" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -902,7 +2084,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="20" t="n">
         <v>300</v>
       </c>
     </row>
@@ -912,7 +2094,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="18">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -930,7 +2112,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -940,7 +2122,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -950,7 +2132,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -960,7 +2142,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -970,8 +2152,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
-        <v>1.12</v>
+      <c r="B17" s="22" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="18">
@@ -980,7 +2162,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.04899999999999999</v>
       </c>
     </row>
@@ -990,7 +2172,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.19</v>
       </c>
     </row>
@@ -1007,7 +2189,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1019,34 +2201,59 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
         </is>
       </c>
     </row>
@@ -1056,19 +2263,34 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>0.07474550587629027</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>0.0623091294072177</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0.04987275293814514</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0.03743637646907257</v>
-      </c>
-      <c r="F26" s="14" t="n">
+      <c r="B26" s="11" t="n">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.05725920239965994</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.04812569198804942</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.04157814174388176</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.03688439177613628</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.03351957777118297</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.03110743963733855</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.02937824736454688</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.02813863928641545</v>
+      </c>
+      <c r="K26" s="11" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1078,20 +2300,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0.2837500000000001</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>0.2825</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>0.28</v>
+      <c r="B27" s="11" t="n">
+        <v>0.2869081058999161</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.2862906156470625</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.285673125394209</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.2850556351413554</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.2844381448885019</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.2838206546356483</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.2832031643827948</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.2825856741299412</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.2825856741299412</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.2825856741299412</v>
       </c>
     </row>
     <row r="28">
@@ -1100,19 +2337,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.052</v>
       </c>
     </row>
@@ -1122,20 +2374,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.04800000000000001</v>
       </c>
-      <c r="C29" s="14" t="n">
-        <v>0.04800000000000001</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>0.04800000000000001</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>0.04800000000000001</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>0.04800000000000001</v>
+      <c r="C29" s="11" t="n">
+        <v>0.04902222222222223</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.05004444444444445</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.05106666666666667</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.05208888888888889</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.05311111111111112</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.05413333333333334</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.05515555555555555</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.05617777777777778</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.0572</v>
       </c>
     </row>
     <row r="30">
@@ -1144,7 +2411,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.1647705627705626</v>
       </c>
     </row>
@@ -1153,7 +2420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1208,7 +2475,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -1219,7 +2486,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1230,7 +2497,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -1241,18 +2508,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -1262,13 +2529,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1281,6 +2548,11 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1298,54 +2570,79 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2022A</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2023A</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2024A</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
         </is>
       </c>
     </row>
@@ -1355,36 +2652,56 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="25" t="n">
         <v>70174.20000000001</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="25" t="n">
         <v>75086.39400000001</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="25" t="n">
         <v>81093.30552000001</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="25" t="n">
         <v>85958.90385120003</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="18">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="18">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="18">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="18">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="18">
         <f>I5*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="K5" s="18">
+        <f>J5*(1+Assumptions!G$26)</f>
+        <v/>
+      </c>
+      <c r="L5" s="18">
+        <f>K5*(1+Assumptions!H$26)</f>
+        <v/>
+      </c>
+      <c r="M5" s="18">
+        <f>L5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="18">
+        <f>M5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="O5" s="18">
+        <f>N5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -1394,36 +2711,56 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="26">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>L5/K5-1</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>O5/N5-1</f>
         <v/>
       </c>
     </row>
@@ -1433,36 +2770,56 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="25" t="n">
         <v>18947.034</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="25" t="n">
         <v>20648.75835000001</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="25" t="n">
         <v>22706.12554560001</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="25" t="n">
         <v>24498.28759759201</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="18">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="18">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="18">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="18">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="18">
         <f>J5*Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="K7" s="18">
+        <f>K5*Assumptions!G$27</f>
+        <v/>
+      </c>
+      <c r="L7" s="18">
+        <f>L5*Assumptions!H$27</f>
+        <v/>
+      </c>
+      <c r="M7" s="18">
+        <f>M5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="18">
+        <f>N5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="O7" s="18">
+        <f>O5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -1472,40 +2829,60 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="12">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="12">
         <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>L7/L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>O7/O5</f>
         <v/>
       </c>
     </row>
@@ -1515,36 +2892,56 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="25" t="n">
         <v>3649.0584</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="25" t="n">
         <v>3904.492488</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="25" t="n">
         <v>4216.85188704</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="25" t="n">
         <v>4469.863000262401</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="18">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="18">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="18">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="18">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="18">
         <f>J5*Assumptions!F$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="18">
+        <f>K5*Assumptions!G$28</f>
+        <v/>
+      </c>
+      <c r="L9" s="18">
+        <f>L5*Assumptions!H$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="18">
+        <f>M5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="18">
+        <f>N5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="O9" s="18">
+        <f>O5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -1554,40 +2951,60 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="27">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="18">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="18">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="18">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="18">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="18">
         <f>J7+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="18">
+        <f>K7+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="18">
+        <f>L7+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="18">
+        <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="18">
+        <f>N7+N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="18">
+        <f>O7+O9</f>
         <v/>
       </c>
     </row>
@@ -1597,40 +3014,60 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="28">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="23">
         <f>J7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>K7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="L11" s="23">
+        <f>L7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="M11" s="23">
+        <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>O7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -1640,36 +3077,56 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="25" t="n">
         <v>3368.361600000001</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="25" t="n">
         <v>3604.146912000001</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="25" t="n">
         <v>3892.478664960001</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="25" t="n">
         <v>4126.027384857602</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="18">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="18">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="18">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="18">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="18">
         <f>J5*Assumptions!F$29</f>
+        <v/>
+      </c>
+      <c r="K12" s="18">
+        <f>K5*Assumptions!G$29</f>
+        <v/>
+      </c>
+      <c r="L12" s="18">
+        <f>L5*Assumptions!H$29</f>
+        <v/>
+      </c>
+      <c r="M12" s="18">
+        <f>M5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="18">
+        <f>N5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="O12" s="18">
+        <f>O5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -1679,79 +3136,119 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="25" t="n">
         <v>842.0904000000003</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="25" t="n">
         <v>901.0367280000003</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="25" t="n">
         <v>973.1196662400002</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="25" t="n">
         <v>1031.5068462144</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="18">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="18">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="18">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="18">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="18">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="K13" s="18">
+        <f>(K5-J5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="L13" s="18">
+        <f>(L5-K5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="M13" s="18">
+        <f>(M5-L5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="N13" s="18">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="O13" s="18">
+        <f>(O5-N5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="30">
         <f>J11+J9-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>K11+K9-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>L11+L9-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="30">
+        <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="30">
+        <f>O11+O9-O12-O13</f>
         <v/>
       </c>
     </row>
@@ -1760,13 +3257,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1776,6 +3273,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1793,34 +3295,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
         </is>
       </c>
     </row>
@@ -1830,24 +3357,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="23">
         <f>Model!J14</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Model!K14</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Model!L14</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!N14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!O14</f>
         <v/>
       </c>
     </row>
@@ -1857,20 +3404,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -1879,24 +3441,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>1/(1+WACC!$B$10)^G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>1/(1+WACC!$B$10)^H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -1906,24 +3488,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="18">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="18">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="18">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="18">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="18">
         <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="18">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="18">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="18">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -1933,8 +3535,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="10">
-        <f>SUM(B8:F8)</f>
+      <c r="B10" s="18">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -1944,8 +3546,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="17">
-        <f>Model!J11</f>
+      <c r="B11" s="23">
+        <f>Model!O11</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +3557,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="20" t="n">
         <v>37500</v>
       </c>
     </row>
@@ -1965,8 +3567,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="17">
-        <f>$B$12*Model!J5/Model!E5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!O5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -1976,7 +3578,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -1987,7 +3589,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -1998,7 +3600,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="18">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -2009,8 +3611,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="10">
-        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
+      <c r="B17" s="18">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -2020,18 +3622,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -2042,7 +3644,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -2053,40 +3655,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2096,7 +3698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2128,660 +3730,150 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>0.07724048226164079</v>
-      </c>
-      <c r="B5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F5" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A5" s="15" t="n">
+        <v>0.07604129145865833</v>
+      </c>
+      <c r="B5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>0.0847404822616408</v>
-      </c>
-      <c r="B6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A6" s="15" t="n">
+        <v>0.08354129145865832</v>
+      </c>
+      <c r="B6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
-        <v>0.09224048226164079</v>
-      </c>
-      <c r="B7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A7" s="15" t="n">
+        <v>0.09104129145865833</v>
+      </c>
+      <c r="B7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>0.09974048226164078</v>
-      </c>
-      <c r="B8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+      <c r="A8" s="15" t="n">
+        <v>0.09854129145865834</v>
+      </c>
+      <c r="B8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
-        <v>0.1072404822616408</v>
-      </c>
-      <c r="B9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Multi-stage dividend discount</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dividends fade from the retention-implied growth to terminal g, at Ke.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Current DPS (USD)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Near-term dividend growth</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="B6" s="29">
-        <f>Assumptions!$B$22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity (Ke)</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>WACC!$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Growth (fade)</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>$B$5+($B$6-$B$5)*0/5</f>
-        <v/>
-      </c>
-      <c r="C10" s="18">
-        <f>$B$5+($B$6-$B$5)*1/5</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
-        <f>$B$5+($B$6-$B$5)*2/5</f>
-        <v/>
-      </c>
-      <c r="E10" s="18">
-        <f>$B$5+($B$6-$B$5)*3/5</f>
-        <v/>
-      </c>
-      <c r="F10" s="18">
-        <f>$B$5+($B$6-$B$5)*4/5</f>
-        <v/>
-      </c>
-      <c r="G10" s="18">
-        <f>$B$5+($B$6-$B$5)*5/5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DPS</t>
-        </is>
-      </c>
-      <c r="B11" s="32">
-        <f>$B$4*(1+B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>B11*(1+C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>C11*(1+D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="32">
-        <f>D11*(1+E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>E11*(1+F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="32">
-        <f>F11*(1+G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>PV of DPS</t>
-        </is>
-      </c>
-      <c r="B12" s="32">
-        <f>B11/(1+$B$7)^1</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>C11/(1+$B$7)^2</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>D11/(1+$B$7)^3</f>
-        <v/>
-      </c>
-      <c r="E12" s="32">
-        <f>E11/(1+$B$7)^4</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>F11/(1+$B$7)^5</f>
-        <v/>
-      </c>
-      <c r="G12" s="32">
-        <f>G11/(1+$B$7)^6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>PV explicit dividends</t>
-        </is>
-      </c>
-      <c r="B14" s="32">
-        <f>SUM(B12:G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>PV terminal value</t>
-        </is>
-      </c>
-      <c r="B15" s="32">
-        <f>G11*(1+$B$6)/($B$7-$B$6)/(1+$B$7)^6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B16" s="34">
-        <f>$B$14+$B$15</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMO — IS (reported)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>As reported by DEMO (synthetic) (USDmm). Hardcoded actuals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n">
-        <v>58000</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>64380.00000000001</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>70174.20000000001</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>75086.39400000001</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>81093.30552000001</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>85958.90385120003</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>EBIT (operating income)</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>15080</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>17060.7</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>18947.034</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>20648.75835000001</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>22706.12554560001</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>24498.28759759201</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>18096</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>20408.46</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>22596.09240000001</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>24553.25083800001</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>26922.97743264001</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>28968.15059785441</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>3016</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>3347.760000000001</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>3649.0584</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>3904.492488</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>4216.85188704</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>4469.863000262401</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n">
-        <v>550</v>
-      </c>
-      <c r="C9" s="21" t="n">
-        <v>550</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>550</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>550</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>550</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Pre-tax income</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="n">
-        <v>14730</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>16710.7</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>18597.034</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>20298.75835000001</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>22356.12554560001</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>24148.28759759201</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Tax expense</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="n">
-        <v>2798.7</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>3175.033000000001</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>3533.436460000001</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>3856.764086500001</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>4247.663853664001</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>4588.174643542482</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="n">
-        <v>11931.3</v>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>13535.667</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>15063.59754</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>16441.9942635</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>18108.46169193601</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>19560.11295404953</v>
+      <c r="A9" s="15" t="n">
+        <v>0.1060412914586583</v>
+      </c>
+      <c r="B9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2795,167 +3887,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DEMO — BS (reported)</t>
+          <t>Comparable companies</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by DEMO (synthetic) (USDmm). Hardcoded actuals.</t>
+          <t>Peer inputs in blue; medians and implied values are live formulas.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>FY2025</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Peer</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBIT</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>EV/Sales</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>P/E</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Total debt</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>12000</v>
+          <t>PEERA</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n">
+        <v>17.66666666666667</v>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>22.64957264957265</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>2.564516129032258</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>23.87096774193548</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Cash &amp; ST investments</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>10100</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>10700</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>11300</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>11900</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>12500</v>
+          <t>PEERB</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n">
+        <v>16.72131147540984</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>21.43757881462799</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>2.48780487804878</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>23.72549019607843</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>28000</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>36000</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>38000</v>
+          <t>PEERC</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>21.94871794871795</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>2.743589743589744</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>29.43820224719101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Minority interest</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>300</v>
+          <t>PEERD</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>21.36752136752137</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>2.424242424242424</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>20.95238095238095</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PEERE</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>16.82926829268293</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>21.57598499061914</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>2.509090909090909</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>23.78378378378378</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B10" s="37">
+        <f>MEDIAN(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="37">
+        <f>MEDIAN(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="37">
+        <f>MEDIAN(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="37">
+        <f>MEDIAN(E5:E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Company metric</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>×median</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Implied VPS (USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>28968.15059785441</v>
+      </c>
+      <c r="C13" s="38">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="D13" s="4">
+        <f>(B13*C13-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
+        <v>24498.28759759201</v>
+      </c>
+      <c r="C14" s="38">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="D14" s="4">
+        <f>(B14*C14-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>85958.90385120003</v>
+      </c>
+      <c r="C15" s="38">
+        <f>D10</f>
+        <v/>
+      </c>
+      <c r="D15" s="4">
+        <f>(B15*C15-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>12.86849536450627</v>
+      </c>
+      <c r="C16" s="38">
+        <f>E10</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>B16*C16</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/DEMO.xlsx
+++ b/docs/reports/DEMO.xlsx
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>294.2009389878127</v>
+        <v>298.006665307772</v>
       </c>
     </row>
     <row r="8">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>230.2679444300176</v>
+        <v>243.0634455376986</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>195.7932446575796</v>
+        <v>202.3748546056572</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>270.3739636759826</v>
+        <v>291.6140709499754</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0.3888888888888889</v>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>294.2009389878127</v>
+        <v>298.006665307772</v>
       </c>
     </row>
     <row r="20">
@@ -1544,7 +1544,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Target anchored 30% to the Street consensus ($285.00, 24 analysts); model-only target $298.14.</t>
+          <t>Target anchored 30% to the Street consensus ($285.00, 24 analysts); model-only target $303.58.</t>
         </is>
       </c>
     </row>
@@ -1656,31 +1656,31 @@
         <v>91976.02712078404</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>97242.50107360962</v>
+        <v>97954.468883635</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>101922.3637284257</v>
+        <v>103831.7370166531</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>106160.1062143977</v>
+        <v>109542.482552569</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>110075.7571630058</v>
+        <v>115019.6066801975</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>113765.450065953</v>
+        <v>120195.4889808064</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>117304.4019366943</v>
+        <v>125003.3085400386</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>120750.5996737408</v>
+        <v>129378.42433894</v>
       </c>
       <c r="J5" s="18" t="n">
-        <v>124148.3572415785</v>
+        <v>133259.7770691082</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>127252.0661726179</v>
+        <v>136591.2714958359</v>
       </c>
     </row>
     <row r="6">
@@ -1825,31 +1825,31 @@
         <v>20929.320860833</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>22104.5885545333</v>
+        <v>22269.69061368228</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>23138.84895703044</v>
+        <v>23580.66883121206</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>24066.3445679313</v>
+        <v>24847.31857057656</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>24915.3927733605</v>
+        <v>26054.43047543562</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>25708.57745523674</v>
+        <v>27186.8095170953</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>26463.49203784749</v>
+        <v>28229.5793548548</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>27193.63558442294</v>
+        <v>29168.49630034804</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>27971.36325082134</v>
+        <v>30056.91618935849</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>28681.78483209187</v>
+        <v>30819.47659409245</v>
       </c>
     </row>
     <row r="10">
@@ -1909,31 +1909,31 @@
         <v>20305.78018192693</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>21526.39523626225</v>
+        <v>21576.306040602</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>22567.06019833192</v>
+        <v>22815.31678354708</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>23467.17211944108</v>
+        <v>24008.59546516661</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>24260.42425119743</v>
+        <v>25141.7376855238</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>24974.21862353873</v>
+        <v>26200.42593427777</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>25630.12755568923</v>
+        <v>27170.71849549537</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>26244.76841823402</v>
+        <v>28039.34520228492</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>26892.84857617929</v>
+        <v>28860.65378038668</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>27508.67422075087</v>
+        <v>29560.26977075519</v>
       </c>
     </row>
     <row r="13">
@@ -2267,28 +2267,28 @@
         <v>0.07000000000000006</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.05725920239965994</v>
+        <v>0.06500000000000006</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.04812569198804942</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.04157814174388176</v>
+        <v>0.05500000000000005</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.03688439177613628</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.03351957777118297</v>
+        <v>0.04500000000000003</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.03110743963733855</v>
+        <v>0.04000000000000002</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.02937824736454688</v>
+        <v>0.03500000000000002</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.02813863928641545</v>
+        <v>0.03000000000000001</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
